--- a/data/BritishIslesPalaoemag Dataset.xlsx
+++ b/data/BritishIslesPalaoemag Dataset.xlsx
@@ -1,110 +1,198 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rosso\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B084633D-7200-4228-BB17-31C0E0314A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{F23F32CA-3786-4781-85D2-B74D7778852E}"/>
+    <workbookView xWindow="3720" yWindow="2520" windowWidth="21600" windowHeight="11295"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Geologic Area</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Rock type</t>
-  </si>
-  <si>
-    <t>AgeUpBound</t>
-  </si>
-  <si>
-    <t>AgeLowBound</t>
-  </si>
-  <si>
-    <t>nSample</t>
-  </si>
-  <si>
-    <t>Nsites</t>
-  </si>
-  <si>
-    <t>Dec</t>
-  </si>
-  <si>
-    <t>Inc</t>
-  </si>
-  <si>
-    <t>a95</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>A95_VGP</t>
-  </si>
-  <si>
-    <t>K_VGP</t>
-  </si>
-  <si>
-    <t>Plat</t>
-  </si>
-  <si>
-    <t>Lambda</t>
-  </si>
-  <si>
-    <t>Ref</t>
-  </si>
-  <si>
-    <t>DOI</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Plon</t>
-  </si>
-  <si>
-    <t>Slat</t>
-  </si>
-  <si>
-    <t>Slon</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Geologic Area</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Rock type</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>AgeUpBound</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>AgeLowBound</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>nSample</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Nsites</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Dec</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Inc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>a95</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>k</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>A95_VGP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>K_VGP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Slat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Slon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Plat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Plon</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Lambda</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Ref</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>DOI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Comments</t>
+    </r>
+  </si>
+  <si>
+    <t>Scotland</t>
   </si>
   <si>
     <t>Mauchline lavas, Scotland</t>
@@ -116,6 +204,15 @@
     <t>Harcombe-Smee et al. (1996)</t>
   </si>
   <si>
+    <t>10.1016/0031-9201(95)03083-2</t>
+  </si>
+  <si>
+    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Paper is originally on palaeointensity as well.</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
     <t>SW England, Aylesbeare Mudstone</t>
   </si>
   <si>
@@ -125,12 +222,29 @@
     <t>Hounslow et al. (2017)</t>
   </si>
   <si>
+    <t>https://doi.org/10.1144/jgs2015-141</t>
+  </si>
+  <si>
+    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Paper on Kiaman superchron, in paper the number of sites is quoted as 13 with 153 samples but Bram claims it’s 81? Paper then says that it did demagnetised 250 samples?</t>
+  </si>
+  <si>
     <t>Hadrian's Wall–Pennines Sill and Hett Dike (Whin Sill), UK</t>
   </si>
   <si>
+    <r>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
     <t>Liss et al. (2004)</t>
   </si>
   <si>
+    <t xml:space="preserve"> https://doi.org/10.1144/0016-764903-156</t>
+  </si>
+  <si>
+    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Paper says the total number of samples but doesn't split them up by site so nSamples canot be found.</t>
+  </si>
+  <si>
     <t>Holy Island Sill and Dyke (Whin Sill), UK</t>
   </si>
   <si>
@@ -140,63 +254,45 @@
     <t>Torsvik (1985)</t>
   </si>
   <si>
+    <t>10.1016/0031-9201(85)90077-9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taken from Bram (2023) paper, already corrected for tectonic folding. Bram paper has the inclination as positive but paper has it as negative, taken results from the paper directly. </t>
+  </si>
+  <si>
     <t>Great Whin Sill, UK</t>
   </si>
   <si>
     <t>Storetvedt and Gidskehaug (1969)</t>
   </si>
   <si>
+    <t>10.1016/0031-9201(69)90006-5</t>
+  </si>
+  <si>
+    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Can't access original article as behind paywall</t>
+  </si>
+  <si>
     <t>Alnwick Sill, High Green and St. Oswalds Chapel Dyke (Whin Sill), UK</t>
   </si>
   <si>
-    <t>Scotland</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>10.1016/0031-9201(95)03083-2</t>
-  </si>
-  <si>
-    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Paper is originally on palaeointensity as well.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1144/jgs2015-141</t>
-  </si>
-  <si>
-    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Paper on Kiaman superchron, in paper the number of sites is quoted as 13 with 153 samples but Bram claims it’s 81? Paper then says that it did demagnetised 250 samples?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> https://doi.org/10.1144/0016-764903-156</t>
-  </si>
-  <si>
-    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Paper says the total number of samples but doesn't split them up by site so nSamples canot be found.</t>
-  </si>
-  <si>
-    <t>10.1016/0031-9201(85)90077-9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taken from Bram (2023) paper, already corrected for tectonic folding. Bram paper has the inclination as positive but paper has it as negative, taken results from the paper directly. </t>
-  </si>
-  <si>
-    <t>10.1016/0031-9201(69)90006-5</t>
-  </si>
-  <si>
-    <t>Taken from Bram (2023) paper, already corrected for tectonic folding. Can't access original article as behind paywall</t>
+    <t>Kinghorn and Burntisland Lavas, Eastern Midland Valley</t>
+  </si>
+  <si>
+    <t>Torsvik (1988)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/0031-9201(89)90236-6</t>
+  </si>
+  <si>
+    <t>Found with GPMDB, included despite low sample size as part of a wider study that finds agreement with rest of study, by looking at baked contacts of material intruded by dyke.</t>
   </si>
   <si>
     <t>Permo-Carboniferous dykes, Western Midland Valley</t>
   </si>
   <si>
-    <t>Torsvik (1988)</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1016/0031-9201(89)90236-7</t>
   </si>
   <si>
-    <t>Found with GPMDB, included despite low sample size as part of a wider study that finds agreement with rest of study, by looking at baked contacts of material intruded by dyke.</t>
-  </si>
-  <si>
     <t>Upper Triassic, Mercia Mudstone, Somerset</t>
   </si>
   <si>
@@ -206,6 +302,9 @@
     <t xml:space="preserve"> https://doi.org/10.1144/gsjgs.156.2.0317</t>
   </si>
   <si>
+    <t>Found with GPMDB, included but quite suspect. Large variance in dec/inc measurements between sites, possibly inclination shallowing or poor lab measurement.</t>
+  </si>
+  <si>
     <t>Lower-Middle Triassic, Sherwood Sandstone, Devon</t>
   </si>
   <si>
@@ -215,52 +314,44 @@
     <t>https://doi.org/10.1016/S0031-0182(03)00235-9</t>
   </si>
   <si>
-    <t>Found with GPMDB, included but quite suspect. Large variance in dec/inc measurements between sites, possibly inclination shallowing or poor lab measurement.</t>
-  </si>
-  <si>
     <t>Found with GPMDB, not sure why left out of Bram (2023), results seem sensible using ChRM</t>
-  </si>
-  <si>
-    <t>Kinghorn and Burntisland Lavas, Eastern Midland Valley</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/0031-9201(89)90236-6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -286,34 +377,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -645,9 +732,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDAC3882-0CBE-4A5C-B9C0-C57719AD5A5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="50.140625" customWidth="1"/>
     <col min="22" max="22" width="100.5703125" customWidth="1"/>
@@ -697,373 +784,382 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="P1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="Q1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" t="s">
-        <v>15</v>
-      </c>
-      <c r="T1" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" t="s">
-        <v>18</v>
-      </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="2">
+      <c r="D2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="3">
         <v>293</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>279</v>
       </c>
       <c r="G2">
         <v>75</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="4">
         <v>5</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
         <v>191.6</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="3">
         <v>-24.1</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="3">
         <v>18.2</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="3">
         <v>18.5</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2">
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3">
         <v>55.5</v>
       </c>
-      <c r="P2" s="2">
-        <v>-4.5999999999999996</v>
-      </c>
-      <c r="Q2" s="2">
+      <c r="P2" s="3">
+        <v>-4.6</v>
+      </c>
+      <c r="Q2" s="3">
         <v>-46.2</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="3">
         <v>348</v>
       </c>
-      <c r="T2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>38</v>
+      <c r="T2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="V2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="15.75" customHeight="1" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="2">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="3">
         <v>264.3</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>254.2</v>
       </c>
       <c r="G3">
         <v>153</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="4">
         <v>13</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3">
         <v>13.7</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>45.6</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="3">
         <v>3.4</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="3">
         <v>22</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="3">
         <v>3.4</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="3">
         <v>22.4</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="3">
         <v>50.62</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="3">
         <v>-3.41</v>
       </c>
-      <c r="Q3" s="2">
-        <v>-65.599999999999994</v>
-      </c>
-      <c r="R3" s="2">
-        <v>325.89999999999998</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="U3" s="7" t="s">
+      <c r="Q3" s="3">
+        <v>-65.6</v>
+      </c>
+      <c r="R3" s="3">
+        <v>325.9</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="3">
+        <v>296</v>
+      </c>
+      <c r="F4" s="3">
+        <v>292</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="4">
+        <v>47</v>
+      </c>
+      <c r="I4" s="3">
+        <v>9.2</v>
+      </c>
+      <c r="J4" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="K4" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="L4" s="3">
+        <v>35</v>
+      </c>
+      <c r="M4" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="N4" s="3">
+        <v>70.2</v>
+      </c>
+      <c r="O4" s="3">
+        <v>54.8</v>
+      </c>
+      <c r="P4" s="3">
+        <v>-2.5</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>-32.9</v>
+      </c>
+      <c r="R4" s="2">
+        <v>347.1</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U4" t="s">
+        <v>37</v>
+      </c>
+      <c r="V4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" s="3">
+        <v>296</v>
+      </c>
+      <c r="F5" s="3">
+        <v>292</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="4">
+        <v>20</v>
+      </c>
+      <c r="I5" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="J5" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="K5" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="L5" s="3">
+        <v>27.6</v>
+      </c>
+      <c r="M5" s="3">
+        <v>5.5</v>
+      </c>
+      <c r="N5" s="3">
+        <v>36.2</v>
+      </c>
+      <c r="O5" s="3">
+        <v>55.7</v>
+      </c>
+      <c r="P5" s="3">
+        <v>-1.8</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>-35.4</v>
+      </c>
+      <c r="R5" s="2">
+        <v>346.8</v>
+      </c>
+      <c r="T5" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" t="s">
+        <v>37</v>
+      </c>
+      <c r="V5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="V3" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="2">
-        <v>296</v>
-      </c>
-      <c r="F4" s="2">
-        <v>292</v>
-      </c>
-      <c r="H4" s="5">
-        <v>47</v>
-      </c>
-      <c r="I4" s="2">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="J4" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="K4" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="L4" s="2">
-        <v>35</v>
-      </c>
-      <c r="M4" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="N4" s="2">
-        <v>70.2</v>
-      </c>
-      <c r="O4" s="2">
-        <v>54.8</v>
-      </c>
-      <c r="P4" s="2">
-        <v>-2.5</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>-32.9</v>
-      </c>
-      <c r="R4" s="4">
-        <v>347.1</v>
-      </c>
-      <c r="T4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2">
-        <v>296</v>
-      </c>
-      <c r="F5" s="2">
-        <v>292</v>
-      </c>
-      <c r="H5" s="5">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="J5" s="2">
-        <v>2.8</v>
-      </c>
-      <c r="K5" s="2">
-        <v>6.3</v>
-      </c>
-      <c r="L5" s="2">
-        <v>27.6</v>
-      </c>
-      <c r="M5" s="2">
-        <v>5.5</v>
-      </c>
-      <c r="N5" s="2">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="O5" s="2">
-        <v>55.7</v>
-      </c>
-      <c r="P5" s="2">
-        <v>-1.8</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>-35.4</v>
-      </c>
-      <c r="R5" s="4">
-        <v>346.8</v>
-      </c>
-      <c r="T5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="3">
         <v>309</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>285</v>
       </c>
       <c r="G6">
         <v>64</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
         <v>1</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="3">
         <v>192.5</v>
       </c>
-      <c r="J6" s="2">
-        <v>-19.100000000000001</v>
-      </c>
-      <c r="K6" s="2">
+      <c r="J6" s="3">
+        <v>-19.1</v>
+      </c>
+      <c r="K6" s="3">
         <v>1.3</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="3">
         <v>184</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3">
         <v>57.5</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="3">
         <v>-1.8</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="3">
         <v>-41.3</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="3">
         <v>341.8</v>
       </c>
-      <c r="T6" s="6" t="s">
-        <v>32</v>
+      <c r="T6" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="V6" t="s">
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3">
+        <v>296</v>
+      </c>
+      <c r="F7" s="3">
+        <v>292</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="4">
+        <v>5</v>
+      </c>
+      <c r="I7" s="3">
+        <v>13.9</v>
+      </c>
+      <c r="J7" s="3">
+        <v>21.7</v>
+      </c>
+      <c r="K7" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="L7" s="3">
+        <v>259</v>
+      </c>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3">
+        <v>55.5</v>
+      </c>
+      <c r="P7" s="3">
+        <v>-1.7</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>-44.4</v>
+      </c>
+      <c r="R7" s="3">
+        <v>339.1</v>
+      </c>
+      <c r="T7" s="5" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="2">
-        <v>296</v>
-      </c>
-      <c r="F7" s="2">
-        <v>292</v>
-      </c>
-      <c r="H7" s="5">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2">
-        <v>13.9</v>
-      </c>
-      <c r="J7" s="2">
-        <v>21.7</v>
-      </c>
-      <c r="K7" s="2">
-        <v>4.8</v>
-      </c>
-      <c r="L7" s="2">
-        <v>259</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2">
-        <v>55.5</v>
-      </c>
-      <c r="P7" s="2">
-        <v>-1.7</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>-44.4</v>
-      </c>
-      <c r="R7" s="2">
-        <v>339.1</v>
-      </c>
-      <c r="T7" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1072,285 +1168,287 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="3">
+        <v>296</v>
+      </c>
+      <c r="F8" s="3">
+        <v>292</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="4">
+        <v>17</v>
+      </c>
+      <c r="I8" s="3">
+        <v>14.6</v>
+      </c>
+      <c r="J8" s="3">
+        <v>25.6</v>
+      </c>
+      <c r="K8" s="3">
+        <v>8.1</v>
+      </c>
+      <c r="L8" s="3">
+        <v>20.5</v>
+      </c>
+      <c r="M8" s="3">
+        <v>7.7</v>
+      </c>
+      <c r="N8" s="3">
+        <v>47.1</v>
+      </c>
+      <c r="O8" s="3">
+        <v>55.4</v>
+      </c>
+      <c r="P8" s="3">
+        <v>-1.6</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>-47.1</v>
+      </c>
+      <c r="R8" s="3">
+        <v>337.1</v>
+      </c>
+      <c r="T8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="U8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2">
-        <v>296</v>
-      </c>
-      <c r="F8" s="2">
-        <v>292</v>
-      </c>
-      <c r="H8" s="5">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2">
-        <v>14.6</v>
-      </c>
-      <c r="J8" s="2">
-        <v>25.6</v>
-      </c>
-      <c r="K8" s="2">
-        <v>8.1</v>
-      </c>
-      <c r="L8" s="2">
-        <v>20.5</v>
-      </c>
-      <c r="M8" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="N8" s="2">
-        <v>47.1</v>
-      </c>
-      <c r="O8" s="2">
-        <v>55.4</v>
-      </c>
-      <c r="P8" s="2">
-        <v>-1.6</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>-47.1</v>
-      </c>
-      <c r="R8" s="2">
-        <v>337.1</v>
-      </c>
-      <c r="T8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="U8" t="s">
-        <v>42</v>
-      </c>
       <c r="V8" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="2">
+        <v>22</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="3">
         <v>358</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>318</v>
       </c>
       <c r="G9">
         <v>13</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="4">
         <v>1</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>205</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="3">
         <v>-31</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="3">
         <v>7</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="3">
         <v>30.8</v>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2">
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3">
         <v>56.2</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="3">
         <v>-3.1</v>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="T9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" s="7" t="s">
-        <v>61</v>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="T9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U9" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="V9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="2">
+        <v>22</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="3">
         <v>305</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>295</v>
       </c>
       <c r="G10">
         <v>5</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>1</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="3">
         <v>190</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="3">
         <v>-22</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="3">
         <v>6.8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="3">
         <v>85</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="3">
         <v>54.8</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="3">
         <v>-5</v>
       </c>
-      <c r="T10" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" s="7" t="s">
+      <c r="T10" s="5" t="s">
         <v>50</v>
       </c>
+      <c r="U10" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="V10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="2">
+        <v>28</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="3">
         <v>227</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>208</v>
       </c>
       <c r="G11">
         <v>27</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>4</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="3">
         <v>30.8</v>
       </c>
-      <c r="J11" s="2">
-        <v>34.299999999999997</v>
-      </c>
-      <c r="K11" s="2">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="L11" s="2">
+      <c r="J11" s="3">
+        <v>34.3</v>
+      </c>
+      <c r="K11" s="3">
+        <v>5.1</v>
+      </c>
+      <c r="L11" s="3">
         <v>31</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="3">
         <v>51.2</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="3">
         <v>-3.3</v>
       </c>
-      <c r="T11" s="6" t="s">
-        <v>53</v>
+      <c r="T11" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="U11" t="s">
-        <v>54</v>
-      </c>
-      <c r="V11" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="V11" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3">
         <v>251</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>242</v>
       </c>
       <c r="G12">
         <v>138</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="4">
         <v>2</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="3">
         <v>23</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="3">
         <v>34</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="3">
         <v>3.5</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L12" s="3">
         <v>12.8</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O12" s="3">
         <v>51.1</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="3">
         <v>-3.4</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="3">
         <v>-52.8</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="3">
         <v>318.8</v>
       </c>
-      <c r="T12" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>57</v>
+      <c r="T12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="V12" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" display="https://doi.org/10.1016/0031-9201(95)03083-2" xr:uid="{D10B49DE-DB8C-47FD-A6FD-4B924274646F}"/>
-    <hyperlink ref="U3" r:id="rId2" xr:uid="{E92EB8B5-D778-4F58-8037-4261679E81A1}"/>
-    <hyperlink ref="U10" r:id="rId3" xr:uid="{D6B7097B-CE0B-4FBF-A47D-5CE67BFAAAC9}"/>
-    <hyperlink ref="U12" r:id="rId4" xr:uid="{D3BBB145-E366-4F43-AEE4-9BEFD4A4E87A}"/>
-    <hyperlink ref="U9" r:id="rId5" display="https://doi.org/10.1016/0031-9201(89)90236-7" xr:uid="{E69441E3-4E67-40E6-8624-A9DC5E22AFFC}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="U3" r:id="rId2"/>
+    <hyperlink ref="U9" r:id="rId3"/>
+    <hyperlink ref="U10" r:id="rId4"/>
+    <hyperlink ref="U12" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="8" orientation="landscape" r:id="rId6"/>
+  <pageSetup paperSize="8" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/BritishIslesPalaoemag Dataset.xlsx
+++ b/data/BritishIslesPalaoemag Dataset.xlsx
@@ -232,7 +232,7 @@
   </si>
   <si>
     <r>
-      <t>0</t>
+      <t>1</t>
     </r>
   </si>
   <si>
